--- a/slide_classification/SurGen_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/SurGen_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.196708</v>
+        <v>0.163168</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.15093</v>
+        <v>0.156726</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7308,10 +7308,10 @@
         <v>2.7e-05</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>0.216754</v>
+        <v>0.742528</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.343462</v>
+        <v>0.280118</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7394,10 +7394,10 @@
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.513269</v>
+        <v>0.334872</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.460966</v>
+        <v>0.259171</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.497694</v>
+        <v>0.442868</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.425748</v>
+        <v>0.326497</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.331203</v>
+        <v>0.228443</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7609,10 +7609,10 @@
         <v>0.020068</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0.336974</v>
+        <v>0.641216</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.218308</v>
+        <v>0.343464</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.151385</v>
+        <v>0.206819</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>1</v>
       </c>
       <c r="G170" t="n">
-        <v>0.830673</v>
+        <v>0.969913</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>0.585427</v>
+        <v>0.837013</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.352635</v>
+        <v>0.225734</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.347864</v>
+        <v>0.326579</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.401967</v>
+        <v>0.41463</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7953,10 +7953,10 @@
         <v>0.000209</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G175" t="n">
-        <v>0.428288</v>
+        <v>0.621384</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.310381</v>
+        <v>0.324757</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.391768</v>
+        <v>0.402374</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>1</v>
       </c>
       <c r="G178" t="n">
-        <v>0.504975</v>
+        <v>0.744414</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>0.503627</v>
+        <v>0.610722</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>0.561213</v>
+        <v>0.504623</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8211,10 +8211,10 @@
         <v>2.6e-05</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.555422</v>
+        <v>0.36562</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.466002</v>
+        <v>0.28027</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8297,10 +8297,10 @@
         <v>0.002228</v>
       </c>
       <c r="F183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0.284158</v>
+        <v>0.565009</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0.552813</v>
+        <v>0.533191</v>
       </c>
       <c r="H184" t="n">
         <v>1</v>
@@ -8386,7 +8386,7 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0.873858</v>
+        <v>0.877571</v>
       </c>
       <c r="H185" t="n">
         <v>1</v>
@@ -8429,7 +8429,7 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0.563153</v>
+        <v>0.764917</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0.694549</v>
+        <v>0.831954</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>1</v>
       </c>
       <c r="G188" t="n">
-        <v>0.577548</v>
+        <v>0.669723</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0.113031</v>
       </c>
       <c r="F189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.539849</v>
+        <v>0.43992</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>0.236234</v>
+        <v>0.246763</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8641,10 +8641,10 @@
         <v>2.2e-05</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>0.399714</v>
+        <v>0.561464</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.332499</v>
+        <v>0.342563</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8727,10 +8727,10 @@
         <v>0.000108</v>
       </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" t="n">
-        <v>0.445382</v>
+        <v>0.612937</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.42797</v>
+        <v>0.264977</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>1</v>
       </c>
       <c r="G195" t="n">
-        <v>0.592832</v>
+        <v>0.5688260000000001</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.357537</v>
+        <v>0.417059</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>0.305664</v>
+        <v>0.477975</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.50713</v>
+        <v>0.5195419999999999</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>0.456928</v>
+        <v>0.493533</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.479944</v>
+        <v>0.449782</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.405637</v>
+        <v>0.392557</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.26281</v>
+        <v>0.161553</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>0.266248</v>
+        <v>0.169343</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.662798</v>
+        <v>0.662601</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.497046</v>
+        <v>0.328769</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>0</v>
       </c>
       <c r="G206" t="n">
-        <v>0.320918</v>
+        <v>0.321466</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>0.252939</v>
+        <v>0.260623</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.45725</v>
+        <v>0.204585</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.480589</v>
+        <v>0.407353</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>0</v>
       </c>
       <c r="G210" t="n">
-        <v>0.255258</v>
+        <v>0.278188</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.392994</v>
+        <v>0.295663</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>1</v>
       </c>
       <c r="G212" t="n">
-        <v>0.698492</v>
+        <v>0.937324</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>1</v>
       </c>
       <c r="G213" t="n">
-        <v>0.735268</v>
+        <v>0.9779640000000001</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>1</v>
       </c>
       <c r="G214" t="n">
-        <v>0.648513</v>
+        <v>0.768999</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.483163</v>
+        <v>0.413894</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0.558504</v>
+        <v>0.504097</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.378345</v>
+        <v>0.200091</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0.000122</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0.521153</v>
+        <v>0.284213</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9845,10 +9845,10 @@
         <v>0.002025</v>
       </c>
       <c r="F219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.526775</v>
+        <v>0.372585</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.251258</v>
+        <v>0.227821</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9931,10 +9931,10 @@
         <v>0.000507</v>
       </c>
       <c r="F221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0.535223</v>
+        <v>0.411329</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="G222" t="n">
-        <v>0.572557</v>
+        <v>0.681299</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10017,10 +10017,10 @@
         <v>0.805626</v>
       </c>
       <c r="F223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.5104300000000001</v>
+        <v>0.431331</v>
       </c>
       <c r="H223" t="n">
         <v>1</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.414579</v>
+        <v>0.416922</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0.41135</v>
+        <v>0.390271</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.349727</v>
+        <v>0.209944</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0.297715</v>
+        <v>0.272806</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>1</v>
       </c>
       <c r="G228" t="n">
-        <v>0.676145</v>
+        <v>0.818948</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.42193</v>
+        <v>0.342304</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>1</v>
       </c>
       <c r="G230" t="n">
-        <v>0.629416</v>
+        <v>0.597774</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10361,10 +10361,10 @@
         <v>0.159352</v>
       </c>
       <c r="F231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G231" t="n">
-        <v>0.579473</v>
+        <v>0.39404</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.209866</v>
+        <v>0.166536</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>0.27251</v>
+        <v>0.200385</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.453109</v>
+        <v>0.334534</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>0.443426</v>
+        <v>0.446398</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.299274</v>
+        <v>0.376726</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.43611</v>
+        <v>0.362303</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.320693</v>
+        <v>0.200725</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>1</v>
       </c>
       <c r="G239" t="n">
-        <v>0.6055</v>
+        <v>0.684555</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.47791</v>
+        <v>0.352603</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10791,10 +10791,10 @@
         <v>0.30672</v>
       </c>
       <c r="F241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G241" t="n">
-        <v>0.463705</v>
+        <v>0.510177</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.390855</v>
+        <v>0.391733</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.230692</v>
+        <v>0.147754</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>0.407742</v>
+        <v>0.231244</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
         <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>0.437437</v>
+        <v>0.398192</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>0</v>
       </c>
       <c r="G246" t="n">
-        <v>0.426222</v>
+        <v>0.46043</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -11052,7 +11052,7 @@
         <v>0</v>
       </c>
       <c r="G247" t="n">
-        <v>0.316114</v>
+        <v>0.291176</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0.584801</v>
+        <v>0.541546</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.55929</v>
+        <v>0.550337</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.416743</v>
+        <v>0.463028</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.259092</v>
+        <v>0.221158</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>0</v>
       </c>
       <c r="G252" t="n">
-        <v>0.280763</v>
+        <v>0.386249</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.323199</v>
+        <v>0.281253</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.341902</v>
+        <v>0.16851</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>0.224816</v>
+        <v>0.108151</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>0</v>
       </c>
       <c r="G256" t="n">
-        <v>0.395609</v>
+        <v>0.338614</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -11482,7 +11482,7 @@
         <v>0</v>
       </c>
       <c r="G257" t="n">
-        <v>0.367575</v>
+        <v>0.240398</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -11525,7 +11525,7 @@
         <v>0</v>
       </c>
       <c r="G258" t="n">
-        <v>0.419613</v>
+        <v>0.30605</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0.655305</v>
+        <v>0.679243</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11608,10 +11608,10 @@
         <v>0.124066</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G260" t="n">
-        <v>0.479507</v>
+        <v>0.760001</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>0.424114</v>
+        <v>0.335065</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
         <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>0.406305</v>
+        <v>0.277922</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.241834</v>
+        <v>0.239284</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11780,10 +11780,10 @@
         <v>0.121087</v>
       </c>
       <c r="F264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G264" t="n">
-        <v>0.540207</v>
+        <v>0.448543</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.350408</v>
+        <v>0.200609</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11866,10 +11866,10 @@
         <v>0.039848</v>
       </c>
       <c r="F266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G266" t="n">
-        <v>0.445677</v>
+        <v>0.607479</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.659002</v>
+        <v>0.91759</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>0</v>
       </c>
       <c r="G268" t="n">
-        <v>0.251851</v>
+        <v>0.193589</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.285368</v>
+        <v>0.174204</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.374563</v>
+        <v>0.357184</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.328285</v>
+        <v>0.211394</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0.362006</v>
+        <v>0.25574</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>0.602447</v>
+        <v>0.679079</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>0.295445</v>
+        <v>0.231711</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.311785</v>
+        <v>0.294076</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>0</v>
       </c>
       <c r="G276" t="n">
-        <v>0.276312</v>
+        <v>0.189178</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0.293907</v>
+        <v>0.291983</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>0.17033</v>
+        <v>0.149226</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.392086</v>
+        <v>0.232873</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.358546</v>
+        <v>0.461168</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.492747</v>
+        <v>0.388069</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.475028</v>
+        <v>0.292053</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.285162</v>
+        <v>0.270626</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.312435</v>
+        <v>0.257453</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.337414</v>
+        <v>0.39287</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>0.326126</v>
+        <v>0.264633</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12772,7 +12772,7 @@
         <v>0</v>
       </c>
       <c r="G287" t="n">
-        <v>0.363322</v>
+        <v>0.318374</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0.466076</v>
+        <v>0.390986</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>1</v>
       </c>
       <c r="G289" t="n">
-        <v>0.642491</v>
+        <v>0.766441</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12898,10 +12898,10 @@
         <v>0.000625</v>
       </c>
       <c r="F290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>0.366843</v>
+        <v>0.575628</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.220316</v>
+        <v>0.227586</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0.383129</v>
+        <v>0.334304</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0.418409</v>
+        <v>0.340359</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.363473</v>
+        <v>0.14553</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.437756</v>
+        <v>0.428334</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>0</v>
       </c>
       <c r="G296" t="n">
-        <v>0.497092</v>
+        <v>0.487658</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -13202,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="G297" t="n">
-        <v>0.337411</v>
+        <v>0.228178</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.367638</v>
+        <v>0.257057</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>0.342757</v>
+        <v>0.267523</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13328,10 +13328,10 @@
         <v>0.017879</v>
       </c>
       <c r="F300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0.3697</v>
+        <v>0.527051</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.353927</v>
+        <v>0.286015</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>0.218298</v>
+        <v>0.094611</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
         <v>0</v>
       </c>
       <c r="G303" t="n">
-        <v>0.392081</v>
+        <v>0.296924</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -13503,7 +13503,7 @@
         <v>0</v>
       </c>
       <c r="G304" t="n">
-        <v>0.370236</v>
+        <v>0.258635</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.405719</v>
+        <v>0.174728</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.398029</v>
+        <v>0.253183</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -13632,7 +13632,7 @@
         <v>1</v>
       </c>
       <c r="G307" t="n">
-        <v>0.521115</v>
+        <v>0.553111</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13672,10 +13672,10 @@
         <v>8.500000000000001e-05</v>
       </c>
       <c r="F308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0.559219</v>
+        <v>0.473876</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13718,7 +13718,7 @@
         <v>0</v>
       </c>
       <c r="G309" t="n">
-        <v>0.266151</v>
+        <v>0.274298</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -13758,10 +13758,10 @@
         <v>0.00675</v>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.56407</v>
+        <v>0.329528</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13801,10 +13801,10 @@
         <v>0.003216</v>
       </c>
       <c r="F311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.5060170000000001</v>
+        <v>0.337977</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.430309</v>
+        <v>0.364233</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>1</v>
       </c>
       <c r="G313" t="n">
-        <v>0.528447</v>
+        <v>0.550845</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.311607</v>
+        <v>0.301479</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.277938</v>
+        <v>0.201053</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.226814</v>
+        <v>0.257475</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.373179</v>
+        <v>0.388416</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14105,7 +14105,7 @@
         <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>0.453982</v>
+        <v>0.492387</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.426452</v>
+        <v>0.421907</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>0</v>
       </c>
       <c r="G320" t="n">
-        <v>0.324158</v>
+        <v>0.372537</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.310594</v>
+        <v>0.250322</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14274,10 +14274,10 @@
         <v>0.152983</v>
       </c>
       <c r="F322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.579189</v>
+        <v>0.489544</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.323483</v>
+        <v>0.377135</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.478167</v>
+        <v>0.350036</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.442209</v>
+        <v>0.19737</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>0.7095129999999999</v>
+        <v>0.704645</v>
       </c>
       <c r="H326" t="n">
         <v>1</v>
@@ -14489,10 +14489,10 @@
         <v>0.000429</v>
       </c>
       <c r="F327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0.391713</v>
+        <v>0.511279</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14532,10 +14532,10 @@
         <v>0.000915</v>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G328" t="n">
-        <v>0.5697489999999999</v>
+        <v>0.486151</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>0.724057</v>
+        <v>0.635674</v>
       </c>
       <c r="H329" t="n">
         <v>1</v>
@@ -14618,10 +14618,10 @@
         <v>0.460653</v>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.531633</v>
+        <v>0.45829</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.848996</v>
+        <v>0.624654</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.302122</v>
+        <v>0.22164</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>0</v>
       </c>
       <c r="G333" t="n">
-        <v>0.365973</v>
+        <v>0.288042</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -14793,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.294425</v>
+        <v>0.223574</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.428899</v>
+        <v>0.322745</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.413936</v>
+        <v>0.370815</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>1</v>
       </c>
       <c r="G337" t="n">
-        <v>0.511405</v>
+        <v>0.621552</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>0.526662</v>
+        <v>0.6494490000000001</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.198671</v>
+        <v>0.317923</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15048,10 +15048,10 @@
         <v>0.029078</v>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.523763</v>
+        <v>0.320884</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.152556</v>
+        <v>0.16128</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.137801</v>
+        <v>0.155932</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.352878</v>
+        <v>0.317052</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.269501</v>
+        <v>0.212899</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0.765582</v>
+        <v>0.82983</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.164142</v>
+        <v>0.316154</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15349,10 +15349,10 @@
         <v>0.001468</v>
       </c>
       <c r="F347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.509742</v>
+        <v>0.415626</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0.426517</v>
+        <v>0.339866</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>0.245841</v>
+        <v>0.158736</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>0.343507</v>
+        <v>0.235168</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.27221</v>
+        <v>0.232743</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15564,10 +15564,10 @@
         <v>1e-05</v>
       </c>
       <c r="F352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>0.499845</v>
+        <v>0.50831</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>0.576098</v>
+        <v>0.637078</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>0.618237</v>
+        <v>0.636337</v>
       </c>
       <c r="H354" t="n">
         <v>1</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.454985</v>
+        <v>0.325471</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>0.76831</v>
+        <v>0.600977</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.371874</v>
+        <v>0.412838</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>0.603143</v>
+        <v>0.761029</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0.719394</v>
+        <v>0.856258</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0.716757</v>
+        <v>0.703548</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0.6312449999999999</v>
+        <v>0.596604</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0.541049</v>
+        <v>0.680254</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>0.744617</v>
+        <v>0.541828</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16080,10 +16080,10 @@
         <v>0.001116</v>
       </c>
       <c r="F364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>0.579019</v>
+        <v>0.458376</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.418977</v>
+        <v>0.312234</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0.002985</v>
       </c>
       <c r="F366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.5608</v>
+        <v>0.457923</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16209,10 +16209,10 @@
         <v>0.000258</v>
       </c>
       <c r="F367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.5053800000000001</v>
+        <v>0.408446</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.45772</v>
+        <v>0.280812</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.41639</v>
+        <v>0.325442</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.467083</v>
+        <v>0.375719</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>0</v>
       </c>
       <c r="G371" t="n">
-        <v>0.411085</v>
+        <v>0.352518</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16424,10 +16424,10 @@
         <v>0.2879</v>
       </c>
       <c r="F372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0.474336</v>
+        <v>0.54191</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.345075</v>
+        <v>0.298328</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.364926</v>
+        <v>0.331029</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.396235</v>
+        <v>0.307218</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.431633</v>
+        <v>0.473509</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.390306</v>
+        <v>0.299519</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.356787</v>
+        <v>0.302143</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>1</v>
       </c>
       <c r="G379" t="n">
-        <v>0.630175</v>
+        <v>0.660061</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>0</v>
       </c>
       <c r="G380" t="n">
-        <v>0.377644</v>
+        <v>0.329534</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.435471</v>
+        <v>0.333198</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16854,10 +16854,10 @@
         <v>0.00198</v>
       </c>
       <c r="F382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G382" t="n">
-        <v>0.491061</v>
+        <v>0.522533</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.45557</v>
+        <v>0.422192</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.407414</v>
+        <v>0.29048</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.426359</v>
+        <v>0.41354</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.389097</v>
+        <v>0.354121</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.36392</v>
+        <v>0.387512</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.404577</v>
+        <v>0.362291</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.439983</v>
+        <v>0.432551</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.365554</v>
+        <v>0.385845</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>1</v>
       </c>
       <c r="G391" t="n">
-        <v>0.526572</v>
+        <v>0.608707</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17284,10 +17284,10 @@
         <v>0.000317</v>
       </c>
       <c r="F392" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0.444564</v>
+        <v>0.650356</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.523718</v>
+        <v>0.503379</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.409113</v>
+        <v>0.453046</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>0</v>
       </c>
       <c r="G395" t="n">
-        <v>0.496078</v>
+        <v>0.429475</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.291621</v>
+        <v>0.352641</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>0</v>
       </c>
       <c r="G397" t="n">
-        <v>0.481169</v>
+        <v>0.465655</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.360725</v>
+        <v>0.305222</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.357419</v>
+        <v>0.31477</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.315138</v>
+        <v>0.271523</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.361546</v>
+        <v>0.339624</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.364737</v>
+        <v>0.31228</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>0</v>
       </c>
       <c r="G403" t="n">
-        <v>0.393507</v>
+        <v>0.358651</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.314951</v>
+        <v>0.286226</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.352557</v>
+        <v>0.288149</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.381778</v>
+        <v>0.321998</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17929,10 +17929,10 @@
         <v>0</v>
       </c>
       <c r="F407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0.451738</v>
+        <v>0.558968</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
         <v>0</v>
       </c>
       <c r="G408" t="n">
-        <v>0.238087</v>
+        <v>0.314919</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.359186</v>
+        <v>0.430619</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.341743</v>
+        <v>0.347083</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>0.354767</v>
+        <v>0.359337</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0.7854179999999999</v>
+        <v>0.683272</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18187,10 +18187,10 @@
         <v>0.266214</v>
       </c>
       <c r="F413" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G413" t="n">
-        <v>0.444988</v>
+        <v>0.50264</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>0</v>
       </c>
       <c r="G414" t="n">
-        <v>0.363323</v>
+        <v>0.345122</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -18276,7 +18276,7 @@
         <v>0</v>
       </c>
       <c r="G415" t="n">
-        <v>0.274224</v>
+        <v>0.327734</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -18319,7 +18319,7 @@
         <v>0</v>
       </c>
       <c r="G416" t="n">
-        <v>0.365546</v>
+        <v>0.387228</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -18362,7 +18362,7 @@
         <v>0</v>
       </c>
       <c r="G417" t="n">
-        <v>0.329063</v>
+        <v>0.248448</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -18405,7 +18405,7 @@
         <v>0</v>
       </c>
       <c r="G418" t="n">
-        <v>0.413911</v>
+        <v>0.386714</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -18448,7 +18448,7 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>0.573496</v>
+        <v>0.6087590000000001</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -18491,7 +18491,7 @@
         <v>0</v>
       </c>
       <c r="G420" t="n">
-        <v>0.370987</v>
+        <v>0.377606</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -18534,7 +18534,7 @@
         <v>0</v>
       </c>
       <c r="G421" t="n">
-        <v>0.362906</v>
+        <v>0.329672</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -18577,7 +18577,7 @@
         <v>0</v>
       </c>
       <c r="G422" t="n">
-        <v>0.487701</v>
+        <v>0.467397</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -18620,7 +18620,7 @@
         <v>0</v>
       </c>
       <c r="G423" t="n">
-        <v>0.389156</v>
+        <v>0.411977</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -18663,7 +18663,7 @@
         <v>0</v>
       </c>
       <c r="G424" t="n">
-        <v>0.302481</v>
+        <v>0.279865</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -18706,7 +18706,7 @@
         <v>0</v>
       </c>
       <c r="G425" t="n">
-        <v>0.445866</v>
+        <v>0.481456</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -18749,7 +18749,7 @@
         <v>0</v>
       </c>
       <c r="G426" t="n">
-        <v>0.497408</v>
+        <v>0.416575</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -18792,7 +18792,7 @@
         <v>1</v>
       </c>
       <c r="G427" t="n">
-        <v>0.529332</v>
+        <v>0.512073</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -18835,7 +18835,7 @@
         <v>0</v>
       </c>
       <c r="G428" t="n">
-        <v>0.318194</v>
+        <v>0.250546</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -18878,7 +18878,7 @@
         <v>0</v>
       </c>
       <c r="G429" t="n">
-        <v>0.474413</v>
+        <v>0.396261</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -18921,7 +18921,7 @@
         <v>0</v>
       </c>
       <c r="G430" t="n">
-        <v>0.441394</v>
+        <v>0.428395</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -18964,7 +18964,7 @@
         <v>0</v>
       </c>
       <c r="G431" t="n">
-        <v>0.330932</v>
+        <v>0.251157</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -19007,7 +19007,7 @@
         <v>0</v>
       </c>
       <c r="G432" t="n">
-        <v>0.369059</v>
+        <v>0.32528</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -19050,7 +19050,7 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>0.505668</v>
+        <v>0.542942</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -19093,7 +19093,7 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>0.511025</v>
+        <v>0.575058</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -19136,7 +19136,7 @@
         <v>0</v>
       </c>
       <c r="G435" t="n">
-        <v>0.367095</v>
+        <v>0.364218</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -19179,7 +19179,7 @@
         <v>0</v>
       </c>
       <c r="G436" t="n">
-        <v>0.279171</v>
+        <v>0.240331</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -19222,7 +19222,7 @@
         <v>0</v>
       </c>
       <c r="G437" t="n">
-        <v>0.366067</v>
+        <v>0.371425</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -19265,7 +19265,7 @@
         <v>0</v>
       </c>
       <c r="G438" t="n">
-        <v>0.39853</v>
+        <v>0.390899</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -19308,7 +19308,7 @@
         <v>0</v>
       </c>
       <c r="G439" t="n">
-        <v>0.487526</v>
+        <v>0.421084</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -19351,7 +19351,7 @@
         <v>0</v>
       </c>
       <c r="G440" t="n">
-        <v>0.418237</v>
+        <v>0.42167</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -19394,7 +19394,7 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>0.566319</v>
+        <v>0.567715</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -19437,7 +19437,7 @@
         <v>0</v>
       </c>
       <c r="G442" t="n">
-        <v>0.440117</v>
+        <v>0.398418</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>0</v>
       </c>
       <c r="G443" t="n">
-        <v>0.306399</v>
+        <v>0.309824</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -19523,7 +19523,7 @@
         <v>0</v>
       </c>
       <c r="G444" t="n">
-        <v>0.425531</v>
+        <v>0.425299</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -19566,7 +19566,7 @@
         <v>0</v>
       </c>
       <c r="G445" t="n">
-        <v>0.386316</v>
+        <v>0.328518</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -19609,7 +19609,7 @@
         <v>0</v>
       </c>
       <c r="G446" t="n">
-        <v>0.295285</v>
+        <v>0.285347</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -19652,7 +19652,7 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>0.647643</v>
+        <v>0.51486</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -19695,7 +19695,7 @@
         <v>0</v>
       </c>
       <c r="G448" t="n">
-        <v>0.389252</v>
+        <v>0.335178</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -19738,7 +19738,7 @@
         <v>0</v>
       </c>
       <c r="G449" t="n">
-        <v>0.365098</v>
+        <v>0.318238</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -19781,7 +19781,7 @@
         <v>0</v>
       </c>
       <c r="G450" t="n">
-        <v>0.335657</v>
+        <v>0.255885</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -19824,7 +19824,7 @@
         <v>0</v>
       </c>
       <c r="G451" t="n">
-        <v>0.389991</v>
+        <v>0.352469</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -19867,7 +19867,7 @@
         <v>0</v>
       </c>
       <c r="G452" t="n">
-        <v>0.360781</v>
+        <v>0.415978</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -19910,7 +19910,7 @@
         <v>0</v>
       </c>
       <c r="G453" t="n">
-        <v>0.421233</v>
+        <v>0.370933</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -19953,7 +19953,7 @@
         <v>0</v>
       </c>
       <c r="G454" t="n">
-        <v>0.466271</v>
+        <v>0.450572</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -19996,7 +19996,7 @@
         <v>0</v>
       </c>
       <c r="G455" t="n">
-        <v>0.456689</v>
+        <v>0.33935</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -20039,7 +20039,7 @@
         <v>0</v>
       </c>
       <c r="G456" t="n">
-        <v>0.430552</v>
+        <v>0.372934</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -20082,7 +20082,7 @@
         <v>0</v>
       </c>
       <c r="G457" t="n">
-        <v>0.349361</v>
+        <v>0.288743</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -20125,7 +20125,7 @@
         <v>0</v>
       </c>
       <c r="G458" t="n">
-        <v>0.487587</v>
+        <v>0.423507</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -20168,7 +20168,7 @@
         <v>0</v>
       </c>
       <c r="G459" t="n">
-        <v>0.41075</v>
+        <v>0.35407</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -20211,7 +20211,7 @@
         <v>0</v>
       </c>
       <c r="G460" t="n">
-        <v>0.404826</v>
+        <v>0.380703</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -20254,7 +20254,7 @@
         <v>0</v>
       </c>
       <c r="G461" t="n">
-        <v>0.452271</v>
+        <v>0.323218</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -20297,7 +20297,7 @@
         <v>0</v>
       </c>
       <c r="G462" t="n">
-        <v>0.429934</v>
+        <v>0.40428</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -20337,10 +20337,10 @@
         <v>0.002555</v>
       </c>
       <c r="F463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G463" t="n">
-        <v>0.462602</v>
+        <v>0.527068</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -20383,7 +20383,7 @@
         <v>0</v>
       </c>
       <c r="G464" t="n">
-        <v>0.322021</v>
+        <v>0.343255</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -20426,7 +20426,7 @@
         <v>0</v>
       </c>
       <c r="G465" t="n">
-        <v>0.48384</v>
+        <v>0.419202</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -20466,10 +20466,10 @@
         <v>3.1e-05</v>
       </c>
       <c r="F466" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G466" t="n">
-        <v>0.511167</v>
+        <v>0.469049</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -20512,7 +20512,7 @@
         <v>0</v>
       </c>
       <c r="G467" t="n">
-        <v>0.352383</v>
+        <v>0.368416</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -20552,10 +20552,10 @@
         <v>0.024131</v>
       </c>
       <c r="F468" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G468" t="n">
-        <v>0.572928</v>
+        <v>0.499498</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -20598,7 +20598,7 @@
         <v>0</v>
       </c>
       <c r="G469" t="n">
-        <v>0.390944</v>
+        <v>0.330364</v>
       </c>
       <c r="H469" t="n">
         <v>0</v>
@@ -20641,7 +20641,7 @@
         <v>0</v>
       </c>
       <c r="G470" t="n">
-        <v>0.291712</v>
+        <v>0.241944</v>
       </c>
       <c r="H470" t="n">
         <v>0</v>
@@ -20684,7 +20684,7 @@
         <v>0</v>
       </c>
       <c r="G471" t="n">
-        <v>0.387409</v>
+        <v>0.317779</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -20727,7 +20727,7 @@
         <v>0</v>
       </c>
       <c r="G472" t="n">
-        <v>0.274401</v>
+        <v>0.185789</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -20770,7 +20770,7 @@
         <v>0</v>
       </c>
       <c r="G473" t="n">
-        <v>0.300228</v>
+        <v>0.239341</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -20813,7 +20813,7 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>0.66689</v>
+        <v>0.68289</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -20856,7 +20856,7 @@
         <v>0</v>
       </c>
       <c r="G475" t="n">
-        <v>0.357668</v>
+        <v>0.171046</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -20899,7 +20899,7 @@
         <v>0</v>
       </c>
       <c r="G476" t="n">
-        <v>0.367306</v>
+        <v>0.316103</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -20942,7 +20942,7 @@
         <v>0</v>
       </c>
       <c r="G477" t="n">
-        <v>0.476946</v>
+        <v>0.401317</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -20985,7 +20985,7 @@
         <v>1</v>
       </c>
       <c r="G478" t="n">
-        <v>0.517492</v>
+        <v>0.726531</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -21028,7 +21028,7 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>0.713998</v>
+        <v>0.925539</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
@@ -21071,7 +21071,7 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>0.556515</v>
+        <v>0.803349</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -21114,7 +21114,7 @@
         <v>0</v>
       </c>
       <c r="G481" t="n">
-        <v>0.30167</v>
+        <v>0.349481</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -21157,7 +21157,7 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>0.664222</v>
+        <v>0.976596</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -21197,10 +21197,10 @@
         <v>8.500000000000001e-05</v>
       </c>
       <c r="F483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>0.445824</v>
+        <v>0.622699</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>0</v>
       </c>
       <c r="G484" t="n">
-        <v>0.408082</v>
+        <v>0.47747</v>
       </c>
       <c r="H484" t="n">
         <v>0</v>
@@ -21286,7 +21286,7 @@
         <v>0</v>
       </c>
       <c r="G485" t="n">
-        <v>0.387547</v>
+        <v>0.273528</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>0.504186</v>
+        <v>0.732589</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -21369,10 +21369,10 @@
         <v>0.003472</v>
       </c>
       <c r="F487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0.468002</v>
+        <v>0.637167</v>
       </c>
       <c r="H487" t="n">
         <v>0</v>
@@ -21412,10 +21412,10 @@
         <v>0.079675</v>
       </c>
       <c r="F488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0.369981</v>
+        <v>0.687604</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -21458,7 +21458,7 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0.698049</v>
+        <v>0.881776</v>
       </c>
       <c r="H489" t="n">
         <v>0</v>
@@ -21498,10 +21498,10 @@
         <v>0.523961</v>
       </c>
       <c r="F490" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G490" t="n">
-        <v>0.5649</v>
+        <v>0.459903</v>
       </c>
       <c r="H490" t="n">
         <v>0</v>
@@ -21544,7 +21544,7 @@
         <v>0</v>
       </c>
       <c r="G491" t="n">
-        <v>0.255641</v>
+        <v>0.261132</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -21587,7 +21587,7 @@
         <v>0</v>
       </c>
       <c r="G492" t="n">
-        <v>0.291385</v>
+        <v>0.299994</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -21630,7 +21630,7 @@
         <v>1</v>
       </c>
       <c r="G493" t="n">
-        <v>0.5218469999999999</v>
+        <v>0.647847</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>0</v>
       </c>
       <c r="G494" t="n">
-        <v>0.278181</v>
+        <v>0.231948</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -21716,7 +21716,7 @@
         <v>0</v>
       </c>
       <c r="G495" t="n">
-        <v>0.274816</v>
+        <v>0.156652</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -21759,7 +21759,7 @@
         <v>0</v>
       </c>
       <c r="G496" t="n">
-        <v>0.30811</v>
+        <v>0.208267</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -21802,7 +21802,7 @@
         <v>0</v>
       </c>
       <c r="G497" t="n">
-        <v>0.290923</v>
+        <v>0.176931</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -21845,7 +21845,7 @@
         <v>0</v>
       </c>
       <c r="G498" t="n">
-        <v>0.463733</v>
+        <v>0.313606</v>
       </c>
       <c r="H498" t="n">
         <v>0</v>
@@ -21888,7 +21888,7 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0.73226</v>
+        <v>0.912909</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -21928,10 +21928,10 @@
         <v>3.2e-05</v>
       </c>
       <c r="F500" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G500" t="n">
-        <v>0.545899</v>
+        <v>0.462202</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -21974,7 +21974,7 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0.525877</v>
+        <v>0.608799</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -22017,7 +22017,7 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0.844298</v>
+        <v>0.969507</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="G503" t="n">
-        <v>0.601335</v>
+        <v>0.730645</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -22103,7 +22103,7 @@
         <v>0</v>
       </c>
       <c r="G504" t="n">
-        <v>0.293076</v>
+        <v>0.242185</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -22146,7 +22146,7 @@
         <v>1</v>
       </c>
       <c r="G505" t="n">
-        <v>0.588274</v>
+        <v>0.829472</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -22189,7 +22189,7 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>0.74304</v>
+        <v>0.9626710000000001</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -22232,7 +22232,7 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>0.58174</v>
+        <v>0.889821</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -22275,7 +22275,7 @@
         <v>0</v>
       </c>
       <c r="G508" t="n">
-        <v>0.404504</v>
+        <v>0.212954</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -22318,7 +22318,7 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>0.565594</v>
+        <v>0.708978</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -22361,7 +22361,7 @@
         <v>0</v>
       </c>
       <c r="G510" t="n">
-        <v>0.245289</v>
+        <v>0.152278</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -22404,7 +22404,7 @@
         <v>0</v>
       </c>
       <c r="G511" t="n">
-        <v>0.237506</v>
+        <v>0.249942</v>
       </c>
       <c r="H511" t="n">
         <v>0</v>
@@ -22447,7 +22447,7 @@
         <v>1</v>
       </c>
       <c r="G512" t="n">
-        <v>0.586839</v>
+        <v>0.524434</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -22490,7 +22490,7 @@
         <v>0</v>
       </c>
       <c r="G513" t="n">
-        <v>0.384271</v>
+        <v>0.473776</v>
       </c>
       <c r="H513" t="n">
         <v>1</v>
@@ -22533,7 +22533,7 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>0.675783</v>
+        <v>0.844571</v>
       </c>
       <c r="H514" t="n">
         <v>0</v>
@@ -22576,7 +22576,7 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0.738188</v>
+        <v>0.924735</v>
       </c>
       <c r="H515" t="n">
         <v>0</v>
@@ -22619,7 +22619,7 @@
         <v>0</v>
       </c>
       <c r="G516" t="n">
-        <v>0.339918</v>
+        <v>0.401456</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -22662,7 +22662,7 @@
         <v>0</v>
       </c>
       <c r="G517" t="n">
-        <v>0.385822</v>
+        <v>0.374312</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -22702,10 +22702,10 @@
         <v>0.006005</v>
       </c>
       <c r="F518" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>0.373202</v>
+        <v>0.591769</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -22748,7 +22748,7 @@
         <v>0</v>
       </c>
       <c r="G519" t="n">
-        <v>0.328182</v>
+        <v>0.274956</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -22791,7 +22791,7 @@
         <v>0</v>
       </c>
       <c r="G520" t="n">
-        <v>0.300539</v>
+        <v>0.300014</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -22834,7 +22834,7 @@
         <v>0</v>
       </c>
       <c r="G521" t="n">
-        <v>0.473974</v>
+        <v>0.481853</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -22877,7 +22877,7 @@
         <v>0</v>
       </c>
       <c r="G522" t="n">
-        <v>0.387852</v>
+        <v>0.310379</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -22920,7 +22920,7 @@
         <v>0</v>
       </c>
       <c r="G523" t="n">
-        <v>0.440071</v>
+        <v>0.490961</v>
       </c>
       <c r="H523" t="n">
         <v>0</v>
@@ -22963,7 +22963,7 @@
         <v>0</v>
       </c>
       <c r="G524" t="n">
-        <v>0.350837</v>
+        <v>0.217483</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -23006,7 +23006,7 @@
         <v>0</v>
       </c>
       <c r="G525" t="n">
-        <v>0.378443</v>
+        <v>0.2597</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -23049,7 +23049,7 @@
         <v>0</v>
       </c>
       <c r="G526" t="n">
-        <v>0.323525</v>
+        <v>0.21432</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="G527" t="n">
-        <v>0.470318</v>
+        <v>0.447757</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -23135,7 +23135,7 @@
         <v>0</v>
       </c>
       <c r="G528" t="n">
-        <v>0.474996</v>
+        <v>0.432231</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -23178,7 +23178,7 @@
         <v>0</v>
       </c>
       <c r="G529" t="n">
-        <v>0.360945</v>
+        <v>0.239226</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>0</v>
       </c>
       <c r="G530" t="n">
-        <v>0.353298</v>
+        <v>0.276503</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -23264,7 +23264,7 @@
         <v>0</v>
       </c>
       <c r="G531" t="n">
-        <v>0.443871</v>
+        <v>0.424033</v>
       </c>
       <c r="H531" t="n">
         <v>0</v>
@@ -23307,7 +23307,7 @@
         <v>0</v>
       </c>
       <c r="G532" t="n">
-        <v>0.299735</v>
+        <v>0.198497</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -23350,7 +23350,7 @@
         <v>0</v>
       </c>
       <c r="G533" t="n">
-        <v>0.41108</v>
+        <v>0.211979</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -23393,7 +23393,7 @@
         <v>0</v>
       </c>
       <c r="G534" t="n">
-        <v>0.350136</v>
+        <v>0.173838</v>
       </c>
       <c r="H534" t="n">
         <v>0</v>
@@ -23436,7 +23436,7 @@
         <v>0</v>
       </c>
       <c r="G535" t="n">
-        <v>0.430943</v>
+        <v>0.344548</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -23479,7 +23479,7 @@
         <v>0</v>
       </c>
       <c r="G536" t="n">
-        <v>0.389621</v>
+        <v>0.30212</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -23522,7 +23522,7 @@
         <v>0</v>
       </c>
       <c r="G537" t="n">
-        <v>0.451461</v>
+        <v>0.353936</v>
       </c>
       <c r="H537" t="n">
         <v>0</v>
@@ -23565,7 +23565,7 @@
         <v>0</v>
       </c>
       <c r="G538" t="n">
-        <v>0.378949</v>
+        <v>0.21172</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -23608,7 +23608,7 @@
         <v>0</v>
       </c>
       <c r="G539" t="n">
-        <v>0.352337</v>
+        <v>0.221653</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -23651,7 +23651,7 @@
         <v>0</v>
       </c>
       <c r="G540" t="n">
-        <v>0.414701</v>
+        <v>0.237308</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -23691,10 +23691,10 @@
         <v>0.022571</v>
       </c>
       <c r="F541" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G541" t="n">
-        <v>0.512063</v>
+        <v>0.41233</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -23734,10 +23734,10 @@
         <v>0.015829</v>
       </c>
       <c r="F542" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G542" t="n">
-        <v>0.510706</v>
+        <v>0.397845</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -23780,7 +23780,7 @@
         <v>0</v>
       </c>
       <c r="G543" t="n">
-        <v>0.383163</v>
+        <v>0.314947</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -23823,7 +23823,7 @@
         <v>0</v>
       </c>
       <c r="G544" t="n">
-        <v>0.395779</v>
+        <v>0.37723</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -23866,7 +23866,7 @@
         <v>0</v>
       </c>
       <c r="G545" t="n">
-        <v>0.3558</v>
+        <v>0.183132</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -23909,7 +23909,7 @@
         <v>0</v>
       </c>
       <c r="G546" t="n">
-        <v>0.444383</v>
+        <v>0.347609</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -23952,7 +23952,7 @@
         <v>0</v>
       </c>
       <c r="G547" t="n">
-        <v>0.428671</v>
+        <v>0.283635</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -23995,7 +23995,7 @@
         <v>0</v>
       </c>
       <c r="G548" t="n">
-        <v>0.419491</v>
+        <v>0.332148</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -24035,10 +24035,10 @@
         <v>0.657</v>
       </c>
       <c r="F549" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0.495745</v>
+        <v>0.669393</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -24081,7 +24081,7 @@
         <v>0</v>
       </c>
       <c r="G550" t="n">
-        <v>0.365417</v>
+        <v>0.289125</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -24124,7 +24124,7 @@
         <v>0</v>
       </c>
       <c r="G551" t="n">
-        <v>0.310996</v>
+        <v>0.165153</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -24167,7 +24167,7 @@
         <v>0</v>
       </c>
       <c r="G552" t="n">
-        <v>0.337057</v>
+        <v>0.252145</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -24210,7 +24210,7 @@
         <v>0</v>
       </c>
       <c r="G553" t="n">
-        <v>0.377372</v>
+        <v>0.279101</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -24253,7 +24253,7 @@
         <v>0</v>
       </c>
       <c r="G554" t="n">
-        <v>0.462649</v>
+        <v>0.46693</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="G555" t="n">
-        <v>0.419062</v>
+        <v>0.417435</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -24339,7 +24339,7 @@
         <v>0</v>
       </c>
       <c r="G556" t="n">
-        <v>0.417957</v>
+        <v>0.336054</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -24379,10 +24379,10 @@
         <v>0.007081</v>
       </c>
       <c r="F557" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G557" t="n">
-        <v>0.438638</v>
+        <v>0.504742</v>
       </c>
       <c r="H557" t="n">
         <v>0</v>
@@ -24425,7 +24425,7 @@
         <v>0</v>
       </c>
       <c r="G558" t="n">
-        <v>0.304613</v>
+        <v>0.253916</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>0</v>
       </c>
       <c r="G559" t="n">
-        <v>0.361593</v>
+        <v>0.284169</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -24511,7 +24511,7 @@
         <v>0</v>
       </c>
       <c r="G560" t="n">
-        <v>0.405593</v>
+        <v>0.255624</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -24554,7 +24554,7 @@
         <v>0</v>
       </c>
       <c r="G561" t="n">
-        <v>0.385177</v>
+        <v>0.32833</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -24594,10 +24594,10 @@
         <v>0.000167</v>
       </c>
       <c r="F562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G562" t="n">
-        <v>0.500481</v>
+        <v>0.43705</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -24637,10 +24637,10 @@
         <v>0.671861</v>
       </c>
       <c r="F563" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>0.498339</v>
+        <v>0.718937</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -24683,7 +24683,7 @@
         <v>0</v>
       </c>
       <c r="G564" t="n">
-        <v>0.314431</v>
+        <v>0.423316</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -24726,7 +24726,7 @@
         <v>0</v>
       </c>
       <c r="G565" t="n">
-        <v>0.398717</v>
+        <v>0.436414</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -24766,10 +24766,10 @@
         <v>0.971475</v>
       </c>
       <c r="F566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G566" t="n">
-        <v>0.498305</v>
+        <v>0.619007</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -24812,7 +24812,7 @@
         <v>0</v>
       </c>
       <c r="G567" t="n">
-        <v>0.340942</v>
+        <v>0.187038</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -24855,7 +24855,7 @@
         <v>0</v>
       </c>
       <c r="G568" t="n">
-        <v>0.391559</v>
+        <v>0.301802</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -24895,10 +24895,10 @@
         <v>0.000424</v>
       </c>
       <c r="F569" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G569" t="n">
-        <v>0.505651</v>
+        <v>0.380449</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -24941,7 +24941,7 @@
         <v>0</v>
       </c>
       <c r="G570" t="n">
-        <v>0.425669</v>
+        <v>0.360852</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
         <v>0</v>
       </c>
       <c r="G571" t="n">
-        <v>0.388852</v>
+        <v>0.295426</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -25027,7 +25027,7 @@
         <v>0</v>
       </c>
       <c r="G572" t="n">
-        <v>0.398671</v>
+        <v>0.302993</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="G573" t="n">
-        <v>0.343156</v>
+        <v>0.27195</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -25113,7 +25113,7 @@
         <v>0</v>
       </c>
       <c r="G574" t="n">
-        <v>0.429331</v>
+        <v>0.326298</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="G575" t="n">
-        <v>0.333118</v>
+        <v>0.214698</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -25199,7 +25199,7 @@
         <v>0</v>
       </c>
       <c r="G576" t="n">
-        <v>0.43394</v>
+        <v>0.416921</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -25242,7 +25242,7 @@
         <v>0</v>
       </c>
       <c r="G577" t="n">
-        <v>0.382596</v>
+        <v>0.379423</v>
       </c>
       <c r="H577" t="n">
         <v>0</v>
@@ -25285,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="G578" t="n">
-        <v>0.461873</v>
+        <v>0.32263</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="G579" t="n">
-        <v>0.483842</v>
+        <v>0.471669</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -25371,7 +25371,7 @@
         <v>0</v>
       </c>
       <c r="G580" t="n">
-        <v>0.364687</v>
+        <v>0.330543</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -25411,10 +25411,10 @@
         <v>0.009351999999999999</v>
       </c>
       <c r="F581" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>0.438787</v>
+        <v>0.504534</v>
       </c>
       <c r="H581" t="n">
         <v>0</v>
@@ -25457,7 +25457,7 @@
         <v>0</v>
       </c>
       <c r="G582" t="n">
-        <v>0.407964</v>
+        <v>0.45419</v>
       </c>
       <c r="H582" t="n">
         <v>0</v>
@@ -25500,7 +25500,7 @@
         <v>0</v>
       </c>
       <c r="G583" t="n">
-        <v>0.376715</v>
+        <v>0.204834</v>
       </c>
       <c r="H583" t="n">
         <v>0</v>
@@ -25543,7 +25543,7 @@
         <v>0</v>
       </c>
       <c r="G584" t="n">
-        <v>0.388458</v>
+        <v>0.22379</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -25586,7 +25586,7 @@
         <v>0</v>
       </c>
       <c r="G585" t="n">
-        <v>0.371803</v>
+        <v>0.273194</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -25629,7 +25629,7 @@
         <v>0</v>
       </c>
       <c r="G586" t="n">
-        <v>0.480796</v>
+        <v>0.331279</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -25672,7 +25672,7 @@
         <v>0</v>
       </c>
       <c r="G587" t="n">
-        <v>0.311063</v>
+        <v>0.33608</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="G588" t="n">
-        <v>0.290578</v>
+        <v>0.1877</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -25758,7 +25758,7 @@
         <v>0</v>
       </c>
       <c r="G589" t="n">
-        <v>0.389225</v>
+        <v>0.407998</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -25801,7 +25801,7 @@
         <v>0</v>
       </c>
       <c r="G590" t="n">
-        <v>0.31734</v>
+        <v>0.31897</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -25844,7 +25844,7 @@
         <v>0</v>
       </c>
       <c r="G591" t="n">
-        <v>0.43072</v>
+        <v>0.347459</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -25887,7 +25887,7 @@
         <v>0</v>
       </c>
       <c r="G592" t="n">
-        <v>0.46502</v>
+        <v>0.38918</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -25930,7 +25930,7 @@
         <v>0</v>
       </c>
       <c r="G593" t="n">
-        <v>0.316974</v>
+        <v>0.424172</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -25970,10 +25970,10 @@
         <v>0.667229</v>
       </c>
       <c r="F594" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>0.465704</v>
+        <v>0.583021</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -26016,7 +26016,7 @@
         <v>0</v>
       </c>
       <c r="G595" t="n">
-        <v>0.444033</v>
+        <v>0.393866</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -26059,7 +26059,7 @@
         <v>0</v>
       </c>
       <c r="G596" t="n">
-        <v>0.372171</v>
+        <v>0.285345</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -26102,7 +26102,7 @@
         <v>0</v>
       </c>
       <c r="G597" t="n">
-        <v>0.38532</v>
+        <v>0.324227</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -26145,7 +26145,7 @@
         <v>0</v>
       </c>
       <c r="G598" t="n">
-        <v>0.354089</v>
+        <v>0.252269</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -26188,7 +26188,7 @@
         <v>0</v>
       </c>
       <c r="G599" t="n">
-        <v>0.474178</v>
+        <v>0.46378</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -26231,7 +26231,7 @@
         <v>0</v>
       </c>
       <c r="G600" t="n">
-        <v>0.409118</v>
+        <v>0.485788</v>
       </c>
       <c r="H600" t="n">
         <v>0</v>
@@ -26274,7 +26274,7 @@
         <v>0</v>
       </c>
       <c r="G601" t="n">
-        <v>0.398154</v>
+        <v>0.29308</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -26317,7 +26317,7 @@
         <v>0</v>
       </c>
       <c r="G602" t="n">
-        <v>0.412698</v>
+        <v>0.404753</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -26360,7 +26360,7 @@
         <v>0</v>
       </c>
       <c r="G603" t="n">
-        <v>0.376801</v>
+        <v>0.266171</v>
       </c>
       <c r="H603" t="n">
         <v>0</v>
@@ -26403,7 +26403,7 @@
         <v>0</v>
       </c>
       <c r="G604" t="n">
-        <v>0.380367</v>
+        <v>0.235841</v>
       </c>
       <c r="H604" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
         <v>0</v>
       </c>
       <c r="G605" t="n">
-        <v>0.33637</v>
+        <v>0.266676</v>
       </c>
       <c r="H605" t="n">
         <v>0</v>
@@ -26489,7 +26489,7 @@
         <v>0</v>
       </c>
       <c r="G606" t="n">
-        <v>0.361546</v>
+        <v>0.284648</v>
       </c>
       <c r="H606" t="n">
         <v>0</v>
@@ -26532,7 +26532,7 @@
         <v>0</v>
       </c>
       <c r="G607" t="n">
-        <v>0.365522</v>
+        <v>0.363078</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -26575,7 +26575,7 @@
         <v>0</v>
       </c>
       <c r="G608" t="n">
-        <v>0.377747</v>
+        <v>0.374248</v>
       </c>
       <c r="H608" t="n">
         <v>0</v>
@@ -26618,7 +26618,7 @@
         <v>0</v>
       </c>
       <c r="G609" t="n">
-        <v>0.375529</v>
+        <v>0.345341</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -26661,7 +26661,7 @@
         <v>0</v>
       </c>
       <c r="G610" t="n">
-        <v>0.333983</v>
+        <v>0.209184</v>
       </c>
       <c r="H610" t="n">
         <v>0</v>
@@ -26701,10 +26701,10 @@
         <v>0.0004929999999999999</v>
       </c>
       <c r="F611" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G611" t="n">
-        <v>0.564515</v>
+        <v>0.437223</v>
       </c>
       <c r="H611" t="n">
         <v>0</v>
@@ -26747,7 +26747,7 @@
         <v>0</v>
       </c>
       <c r="G612" t="n">
-        <v>0.349212</v>
+        <v>0.182077</v>
       </c>
       <c r="H612" t="n">
         <v>0</v>
@@ -26790,7 +26790,7 @@
         <v>0</v>
       </c>
       <c r="G613" t="n">
-        <v>0.41837</v>
+        <v>0.438763</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -26833,7 +26833,7 @@
         <v>0</v>
       </c>
       <c r="G614" t="n">
-        <v>0.349959</v>
+        <v>0.258183</v>
       </c>
       <c r="H614" t="n">
         <v>0</v>
@@ -26876,7 +26876,7 @@
         <v>0</v>
       </c>
       <c r="G615" t="n">
-        <v>0.42628</v>
+        <v>0.454662</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -26919,7 +26919,7 @@
         <v>0</v>
       </c>
       <c r="G616" t="n">
-        <v>0.427335</v>
+        <v>0.388734</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>0</v>
       </c>
       <c r="G617" t="n">
-        <v>0.398088</v>
+        <v>0.265953</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -27005,7 +27005,7 @@
         <v>0</v>
       </c>
       <c r="G618" t="n">
-        <v>0.373636</v>
+        <v>0.268758</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -27048,7 +27048,7 @@
         <v>0</v>
       </c>
       <c r="G619" t="n">
-        <v>0.341021</v>
+        <v>0.257342</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -27091,7 +27091,7 @@
         <v>0</v>
       </c>
       <c r="G620" t="n">
-        <v>0.314194</v>
+        <v>0.235713</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -27134,7 +27134,7 @@
         <v>0</v>
       </c>
       <c r="G621" t="n">
-        <v>0.473846</v>
+        <v>0.459684</v>
       </c>
       <c r="H621" t="n">
         <v>0</v>
@@ -27177,7 +27177,7 @@
         <v>0</v>
       </c>
       <c r="G622" t="n">
-        <v>0.386978</v>
+        <v>0.464585</v>
       </c>
       <c r="H622" t="n">
         <v>0</v>
@@ -27220,7 +27220,7 @@
         <v>0</v>
       </c>
       <c r="G623" t="n">
-        <v>0.320383</v>
+        <v>0.278894</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
